--- a/pacjenci/ANNA PALUCH.xlsx
+++ b/pacjenci/ANNA PALUCH.xlsx
@@ -485,12 +485,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -529,7 +529,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -573,7 +573,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,7 +617,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -661,7 +661,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -705,12 +705,12 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -718,17 +718,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/ANNA PALUCH.xlsx
+++ b/pacjenci/ANNA PALUCH.xlsx
@@ -413,323 +413,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>28.06.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy). Ocena zaawansowania klinicznego.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 109 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne i pobudzone metabolicznie węzły chłonne grupy: - 2 A po stronie lewej wielkości 17x18x29 mm SUV max 17,1; -1B po lewej wielkości 10x14 mm SUV max 4,6; -1B po prawej wielkości do 8x12 mm SUV max do 4,6. - 3 po stronie lewej 10 mm SUV max 2,5. Aktywny metabolicznie obszar na górno-grzbietowej ścianie nosogardła, wielkości 19x18mm. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi oraz w węzłach chłonnych, najpewniej własnych obu piersi/guzkach?  wielkości do 12mm, SUV max do 3,8 - do kontroli w badaniu USG/Mammografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Aktywne metabolicznie miękkotkankowe nacieki w topografii krezki pośrodkowo w dolnej części śródbrzusza oraz w podbrzuszu, wielkości do 56x29 mm SUV max do 10,8. Pobudzone metabolicznie węzły chłonne krezkowe wielkości do 18x16mm, SUV max do 3,5. Pobudzenie metaboliczne w powłokach przedniej ściany jamy brzusznej- procesy gojenia  Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 9mm uwapniony konkrement w UKM-ie nerki lewej. Niewielka ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Aktywny metabolicznie obszar w łopatce prawej wielkości 20x11 mm wg PET SUV max 7,9. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Wartości referencyjne: MBPS SUVmax 2,2 Prawy płat wątroby SUVmax do 3,6</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem krezki, łopatki prawej oraz węzłów chłonnych szyi. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>17.1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>20.12.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy). Ocena odpowiedzi po IV cyklu immunochemioterpaii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 101 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Skąpe zgrubienia śluzówki w zatokach szczękowych.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi oraz w węzłach chłonnych, najpewniej własnych obu piersi/guzkach?  wielkości do 12mm, SUV max do 2,3 - jak w badaniu poprzednim. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Obniżenie cieniowania wątroby - jak w stłuszczeniu (22HU). Wzmożenie cieniowania tkanki tłuszczowej krezki,  odcinkowo z pobudzeniem  SUV max do 2,6 [Im  fuz 208]  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym - związany ze stosowanym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 3,0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>30.03.2023</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy). Ocena remisji choroby po zakończeniu immunochemioterpaii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Pobudzenie metaboliczne w topografii skóry i błony śluzowej nosa- zmiany zapalne? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi, SUV max do 2,3.  Śladowe pobudzenie metaboliczne w węzłach chłonnych  własnych obu piersi/w guzkach?  wielkości do 8mm, SUV max do 1,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 5mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka- zmiany odczynowe? Macica z pobudzeniem metabolicznym- związane z fazą cyklu? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 7mm, SUV max 4,4 [Im fuz. 262]- drobny węzeł chłonny?- do weryfikacji.    Wartości referencyjne: MBPS SUVmax do 2,3; Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność niejednoznacznego aktywnego metabolicznie obszaru w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej  - drobny węzeł chłonny? - do weryfikacji.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>4.4</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>18.07.2023</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy). Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 117mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Pobudzenie metaboliczne w topografii skóry i błony śluzowej nosa- zmiany zapalne? Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 4,7- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi.  Śladowe pobudzenie metaboliczne w węźle chłonnym  własnym  piersi lewej /w guzkach?  wielkości do 8mm, SUV max do 0,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Gorsze upowietrznienie szczytu lewego płuca. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 5mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka - zmiany odczynowe? Macica z niejednorodnym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 10mm wg PET, SUV max 5,6 [Im fuz. 261]- drobny węzeł chłonny?- do weryfikacji.    Wartości referencyjne: MBPS SUVmax do 2,3; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność niejednoznacznego aktywnego metabolicznie obszaru w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej  - drobny węzeł chłonny? - opisywany już poprzednio. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5.6</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>01.02.2024</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy). Badanie kontrolne.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 116mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Ostroga kostna przegrody nosowej skierowana na stronę lewą. Przyścienne zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 6mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc. Drobny węzeł chłonny  własny  piersi lewej/guzek  wielkości 12mm.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka - zmiany odczynowe? Macica z niejednorodnym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zwapnienia w topografii krążka międzykręgowego na poziomie Th9/Th10. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 11x9mm wg PET, SUV max 7,5 [Im fuz. 261] - drobny węzeł chłonny?- do weryfikacji.   Wartości referencyjne: MBPS SUVmax do 2,4; Prawy płat wątroby SUVmax do 3,5.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność niejednoznacznego aktywnego metabolicznie obszaru w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej  - drobny węzeł chłonny? - opisywany już poprzednio. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>7.5</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>27.03.2025</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Chłoniak nieziarniczy guzkowaty (grudkowy). Ocena remisji choroby po zakończeniu leczenia podtrzymującego.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 106 mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Ostroga kostna przegrody nosowej skierowana na stronę lewą. Polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej. Niewielkie,, przyścienne zgrubienia błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Symetryczne, mierne pobudzenie metaboliczne w tkance gruczołowej obu piersi SUV max do 2,7.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 6mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc. Drobny węzeł chłonny  własny  piersi lewej/guzek  wielkości 12mm.  Brzuch i miednica: Wzmożony metabolizm FDG w endometrium SUV max 5,8 w niejednorodnie wyznakowanej macicy - czynnościowo?- OM 09.03.2025. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy stłuszczenia. Drobny uwapniony konkrement w UKM-ie nerki prawej. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Drobne węzły chłonne pachwinowe obustronnie.  Układ kostny: Niejednorodne metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4 i Th8. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zwapnienia w topografii krążka międzykręgowego na poziomie Th9/Th10. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Wartości referencyjne: MBPS SUVmax do 2,0; Prawy płat wątroby SUVmax do 3,3.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5.8</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/ANNA PALUCH.xlsx
+++ b/pacjenci/ANNA PALUCH.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 109 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Aktywne i pobudzone metabolicznie węzły chłonne grupy: - 2 A po stronie lewej wielkości 17x18x29 mm SUV max 17,1; -1B po lewej wielkości 10x14 mm SUV max 4,6; -1B po prawej wielkości do 8x12 mm SUV max do 4,6. - 3 po stronie lewej 10 mm SUV max 2,5. Aktywny metabolicznie obszar na górno-grzbietowej ścianie nosogardła, wielkości 19x18mm. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi oraz w węzłach chłonnych, najpewniej własnych obu piersi/guzkach?  wielkości do 12mm, SUV max do 3,8 - do kontroli w badaniu USG/Mammografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Aktywne metabolicznie miękkotkankowe nacieki w topografii krezki pośrodkowo w dolnej części śródbrzusza oraz w podbrzuszu, wielkości do 56x29 mm SUV max do 10,8. Pobudzone metabolicznie węzły chłonne krezkowe wielkości do 18x16mm, SUV max do 3,5. Pobudzenie metaboliczne w powłokach przedniej ściany jamy brzusznej- procesy gojenia  Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 9mm uwapniony konkrement w UKM-ie nerki lewej. Niewielka ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Aktywny metabolicznie obszar w łopatce prawej wielkości 20x11 mm wg PET SUV max 7,9. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Wartości referencyjne: MBPS SUVmax 2,2 Prawy płat wątroby SUVmax do 3,6</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Aktywne i pobudzone metabolicznie węzły chłonne grupy: - 2 A po stronie lewej wielkości 17x18x29 mm SUV max 17,1; -1B po lewej wielkości 10x14 mm SUV max 4,6; -1B po prawej wielkości do 8x12 mm SUV max do 4,6. - 3 po stronie lewej 10 mm SUV max 2,5. Aktywny metabolicznie obszar na górno-grzbietowej ścianie nosogardła, wielkości 19x18mm. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Okrężne zgrubienia błony śluzowej w lewej zatoce szczękowej. Drobne polipowate zgrubienie błony śluzowej w zachyłku zębodołowym prawej zatoki szczękowej.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi oraz w węzłach chłonnych, najpewniej własnych obu piersi/guzkach?  wielkości do 12mm, SUV max do 3,8 - do kontroli w badaniu USG/Mammografii. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie miękkotkankowe nacieki w topografii krezki pośrodkowo w dolnej części śródbrzusza oraz w podbrzuszu, wielkości do 56x29 mm SUV max do 10,8. Pobudzone metabolicznie węzły chłonne krezkowe wielkości do 18x16mm, SUV max do 3,5. Pobudzenie metaboliczne w powłokach przedniej ściany jamy brzusznej- procesy gojenia  Niejednorodny metabolizm FDG w wątrobie. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 9mm uwapniony konkrement w UKM-ie nerki lewej. Niewielka ilość płynu w jamie Douglasa po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w łopatce prawej wielkości 20x11 mm wg PET SUV max 7,9. Poza tym fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem krezki, łopatki prawej oraz węzłów chłonnych szyi. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>17.1</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 101 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Skąpe zgrubienia śluzówki w zatokach szczękowych.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi oraz w węzłach chłonnych, najpewniej własnych obu piersi/guzkach?  wielkości do 12mm, SUV max do 2,3 - jak w badaniu poprzednim. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Obniżenie cieniowania wątroby - jak w stłuszczeniu (22HU). Wzmożenie cieniowania tkanki tłuszczowej krezki,  odcinkowo z pobudzeniem  SUV max do 2,6 [Im  fuz 208]  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym - związany ze stosowanym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Wartości referencyjne: MBPS SUVmax 1,9 Prawy płat wątroby SUVmax do 3,0</t>
+          <t>101</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej. Skąpe zgrubienia śluzówki w zatokach szczękowych.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi oraz w węzłach chłonnych, najpewniej własnych obu piersi/guzkach?  wielkości do 12mm, SUV max do 2,3 - jak w badaniu poprzednim. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Niewielka ilość płynu w jamie Douglasa po stronie prawej. Obniżenie cieniowania wątroby - jak w stłuszczeniu (22HU). Wzmożenie cieniowania tkanki tłuszczowej krezki,  odcinkowo z pobudzeniem  SUV max do 2,6 [Im  fuz 208]</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym - związany ze stosowanym leczeniem? Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 99 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Pobudzenie metaboliczne w topografii skóry i błony śluzowej nosa- zmiany zapalne? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi, SUV max do 2,3.  Śladowe pobudzenie metaboliczne w węzłach chłonnych  własnych obu piersi/w guzkach?  wielkości do 8mm, SUV max do 1,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 5mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka- zmiany odczynowe? Macica z pobudzeniem metabolicznym- związane z fazą cyklu? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 7mm, SUV max 4,4 [Im fuz. 262]- drobny węzeł chłonny?- do weryfikacji.    Wartości referencyjne: MBPS SUVmax do 2,3; Prawy płat wątroby SUVmax do 3,2.</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii skóry i błony śluzowej nosa- zmiany zapalne? Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi, SUV max do 2,3.  Śladowe pobudzenie metaboliczne w węzłach chłonnych  własnych obu piersi/w guzkach?  wielkości do 8mm, SUV max do 1,0. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 5mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne części wpustowej żołądka- zmiany odczynowe? Macica z pobudzeniem metabolicznym- związane z fazą cyklu? Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 7mm, SUV max 4,4 [Im fuz. 262]- drobny węzeł chłonny?- do weryfikacji.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność niejednoznacznego aktywnego metabolicznie obszaru w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej  - drobny węzeł chłonny? - do weryfikacji.  Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>4.4</v>
       </c>
     </row>
@@ -568,20 +668,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 117mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>: Pobudzenie metaboliczne w topografii skóry i błony śluzowej nosa- zmiany zapalne? Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 4,7- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi.  Śladowe pobudzenie metaboliczne w węźle chłonnym  własnym  piersi lewej /w guzkach?  wielkości do 8mm, SUV max do 0,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Gorsze upowietrznienie szczytu lewego płuca. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 5mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka - zmiany odczynowe? Macica z niejednorodnym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 10mm wg PET, SUV max 5,6 [Im fuz. 261]- drobny węzeł chłonny?- do weryfikacji.    Wartości referencyjne: MBPS SUVmax do 2,3; Prawy płat wątroby SUVmax do 3,6.</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne w topografii skóry i błony śluzowej nosa- zmiany zapalne? Pobudzenie metaboliczne na tylnej ścianie nosogardła, SUV max 4,7- do ew. kontroli laryngologicznej.  Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Drobne polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi.  Śladowe pobudzenie metaboliczne w węźle chłonnym  własnym  piersi lewej /w guzkach?  wielkości do 8mm, SUV max do 0,9. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Gorsze upowietrznienie szczytu lewego płuca. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 5mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne części wpustowej żołądka - zmiany odczynowe? Macica z niejednorodnym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 10mm wg PET, SUV max 5,6 [Im fuz. 261]- drobny węzeł chłonny?- do weryfikacji.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność niejednoznacznego aktywnego metabolicznie obszaru w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej  - drobny węzeł chłonny? - opisywany już poprzednio. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="L5" t="n">
         <v>5.6</v>
       </c>
     </row>
@@ -601,20 +726,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 116mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Ostroga kostna przegrody nosowej skierowana na stronę lewą. Przyścienne zgrubienie błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 6mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc. Drobny węzeł chłonny  własny  piersi lewej/guzek  wielkości 12mm.  Brzuch i miednica: Pobudzenie metaboliczne części wpustowej żołądka - zmiany odczynowe? Macica z niejednorodnym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zwapnienia w topografii krążka międzykręgowego na poziomie Th9/Th10. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 11x9mm wg PET, SUV max 7,5 [Im fuz. 261] - drobny węzeł chłonny?- do weryfikacji.   Wartości referencyjne: MBPS SUVmax do 2,4; Prawy płat wątroby SUVmax do 3,5.</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Ostroga kostna przegrody nosowej skierowana na stronę lewą. Przyścienne zgrubienie błony śluzowej w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Mierne, symetryczne pobudzenie metaboliczne w tkance gruczołowej obu piersi.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 6mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc. Drobny węzeł chłonny  własny  piersi lewej/guzek  wielkości 12mm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pobudzenie metaboliczne części wpustowej żołądka - zmiany odczynowe? Macica z niejednorodnym pobudzeniem metabolicznym. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Znaczne obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy nasilonego  stłuszczenia. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Zwiększona ilość płynu w jamie Douglasa po stronie prawej.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zwapnienia w topografii krążka międzykręgowego na poziomie Th9/Th10. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Inne: Aktywny metabolicznie obszar w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej wielkości 11x9mm wg PET, SUV max 7,5 [Im fuz. 261] - drobny węzeł chłonny?- do weryfikacji.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność niejednoznacznego aktywnego metabolicznie obszaru w topografii struktur mięśniowych, w przyleganiu do przednio-przyśrodkowego obrysu głowy prawej kości udowej  - drobny węzeł chłonny? - opisywany już poprzednio. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="L6" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -634,20 +784,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 106 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Ostroga kostna przegrody nosowej skierowana na stronę lewą. Polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej. Niewielkie,, przyścienne zgrubienia błony śluzowej w lewej zatoce szczękowej.  Klatka piersiowa i śródpiersie: Symetryczne, mierne pobudzenie metaboliczne w tkance gruczołowej obu piersi SUV max do 2,7.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 6mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc. Drobny węzeł chłonny  własny  piersi lewej/guzek  wielkości 12mm.  Brzuch i miednica: Wzmożony metabolizm FDG w endometrium SUV max 5,8 w niejednorodnie wyznakowanej macicy - czynnościowo?- OM 09.03.2025. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy stłuszczenia. Drobny uwapniony konkrement w UKM-ie nerki prawej. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Drobne węzły chłonne pachwinowe obustronnie.  Układ kostny: Niejednorodne metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4 i Th8. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zwapnienia w topografii krążka międzykręgowego na poziomie Th9/Th10. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.  Wartości referencyjne: MBPS SUVmax do 2,0; Prawy płat wątroby SUVmax do 3,3.</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hypoplazja prawej zatoki czołowej.  Ostroga kostna przegrody nosowej skierowana na stronę lewą. Polipowate zgrubienie błony śluzowej w prawej zatoce szczękowej. Niewielkie,, przyścienne zgrubienia błony śluzowej w lewej zatoce szczękowej.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Symetryczne, mierne pobudzenie metaboliczne w tkance gruczołowej obu piersi SUV max do 2,7.  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobny 3 mm guzek obwodowo w segmencie 3 płuca prawego. Ok. 6mm obwodowy obszar o typie mlecznej szyby w segm. 3/4 płuca lewego. Pasmowate zmiany miąższowo-włókniste w segm. 5 płuca prawego. Niewielkie obwodowe zmiany włókniste w płatach dolnych obu płuc. Zmiany włókniste w nadprzeponowych segmentach obu płuc. Drobny węzeł chłonny  własny  piersi lewej/guzek  wielkości 12mm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Wzmożony metabolizm FDG w endometrium SUV max 5,8 w niejednorodnie wyznakowanej macicy - czynnościowo?- OM 09.03.2025. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Obniżenie cieniowania wątroby w przeglądowym badaniu TK - cechy stłuszczenia. Drobny uwapniony konkrement w UKM-ie nerki prawej. Wzmożenie cieniowania tkanki tłuszczowej okołokrezkowej. Wydatna przepuklina kresy białej, z zawartością pętli jelitowej. Drobne węzły chłonne pachwinowe obustronnie.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Niejednorodne metabolizm FDG w układzie kostnym objętym badaniem. Cechy uogólnionego zaniku kostnego. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Grubobeleczkowa przebudowa trzonu kręgu Th1 - naczyniak? Niewielkie włamanie blaszki granicznej górnej trzonu Th4 i Th8. Drobne guzki Schmorla w obrębie blaszek granicznych trzonów kręgowych. Zwapnienia w topografii krążka międzykręgowego na poziomie Th9/Th10. Drobne zmiany wytwórcze w stawach żebrowo-poprzecznych. Os sacrum arcuatum. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, wydatne, z mostem kostnym po stronie lewej.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="L7" t="n">
         <v>5.8</v>
       </c>
     </row>
